--- a/capstone/sprint4/26-10-sprint-4-initial-metrics.xlsx
+++ b/capstone/sprint4/26-10-sprint-4-initial-metrics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lewis\Software\Stone-Ocean-Backlogs\capstone\sprint4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fawzm\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B4DF6B6-5D65-4EED-9DDD-E07DE3867B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A5E381-367D-4578-8B4D-C4DEA9C21BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="42">
   <si>
     <t>Name</t>
   </si>
@@ -160,19 +160,13 @@
     <t>Fawz Manzoor</t>
   </si>
   <si>
-    <t xml:space="preserve">Ryan Wandke </t>
-  </si>
-  <si>
     <t xml:space="preserve">Juno Tyne </t>
   </si>
   <si>
     <t>JT</t>
   </si>
   <si>
-    <t>9/22/2026 11:56am</t>
-  </si>
-  <si>
-    <t>RW</t>
+    <t>FM</t>
   </si>
 </sst>
 </file>
@@ -539,7 +533,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26F2F5C-9428-EA43-9432-B11B4A37F6BD}">
   <dimension ref="A1:I1003"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -547,7 +541,7 @@
     <col min="7" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25">
+    <row r="1" spans="1:9" ht="23.5">
       <c r="A1" s="13" t="s">
         <v>12</v>
       </c>
@@ -606,7 +600,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:9" ht="145.5">
+    <row r="8" spans="1:9" ht="146">
       <c r="A8" s="4" t="s">
         <v>0</v>
       </c>
@@ -11672,7 +11666,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25">
+    <row r="1" spans="1:9" ht="23.5">
       <c r="A1" s="13" t="s">
         <v>12</v>
       </c>
@@ -17995,7 +17989,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0AC37C3-57FD-E44A-8B5F-68D0EAC49E65}">
   <dimension ref="A1:I1008"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -18004,7 +17998,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25">
+    <row r="1" spans="1:9" ht="23.5">
       <c r="A1" s="13" t="str">
         <f>Sprint4!A1</f>
         <v>Capacity, Commited, Effort, and Delivered Metric</v>
@@ -24341,7 +24335,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D22623D9-D265-E341-9D40-D4F8180816A9}">
   <dimension ref="A1:I1008"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -24350,7 +24344,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25">
+    <row r="1" spans="1:9" ht="23.5">
       <c r="A1" s="13" t="str">
         <f>Sprint4!A1</f>
         <v>Capacity, Commited, Effort, and Delivered Metric</v>
@@ -30687,7 +30681,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE28E1FE-DF56-8B47-AF8A-1EC59E1B4672}">
   <dimension ref="A1:I1008"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -30696,7 +30690,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25">
+    <row r="1" spans="1:9" ht="23.5">
       <c r="A1" s="13" t="str">
         <f>Sprint4!A1</f>
         <v>Capacity, Commited, Effort, and Delivered Metric</v>
@@ -37033,7 +37027,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14211EDA-4B61-5345-86E3-D319343FC73C}">
   <dimension ref="A1:I1008"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -37042,7 +37036,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25">
+    <row r="1" spans="1:9" ht="23.5">
       <c r="A1" s="13" t="str">
         <f>Sprint4!A1</f>
         <v>Capacity, Commited, Effort, and Delivered Metric</v>
@@ -37053,7 +37047,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="12">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16.5" customHeight="1">
@@ -37090,7 +37084,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -37137,7 +37131,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="7">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
@@ -37146,9 +37140,9 @@
         <f t="shared" ref="G9:H12" si="0">D9/B9</f>
         <v>0</v>
       </c>
-      <c r="H9" s="10" t="e">
+      <c r="H9" s="10">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="I9" s="10">
         <f t="shared" ref="I9:I16" si="1">E9/B9</f>
@@ -37163,7 +37157,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="7">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
@@ -37172,9 +37166,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="10" t="e">
+      <c r="H10" s="10">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="I10" s="10">
         <f t="shared" si="1"/>
@@ -37189,7 +37183,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="7">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -37198,9 +37192,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="10" t="e">
+      <c r="H11" s="10">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="I11" s="10">
         <f t="shared" si="1"/>
@@ -37215,7 +37209,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="7">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -37224,9 +37218,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="10" t="e">
+      <c r="H12" s="10">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="I12" s="10">
         <f t="shared" si="1"/>
@@ -37276,7 +37270,7 @@
       </c>
       <c r="C16" s="7">
         <f>SUM(C9:C14)</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D16" s="7">
         <f>SUM(D9:D14)</f>
@@ -37291,9 +37285,9 @@
         <f t="shared" ref="G16:H16" si="2">D16/B16</f>
         <v>0</v>
       </c>
-      <c r="H16" s="10" t="e">
+      <c r="H16" s="10">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="I16" s="10">
         <f t="shared" si="1"/>
@@ -37333,8 +37327,8 @@
         <v>41</v>
       </c>
       <c r="C20" s="16"/>
-      <c r="D20" s="17" t="s">
-        <v>42</v>
+      <c r="D20" s="17">
+        <v>46301.510416666664</v>
       </c>
       <c r="E20" s="3"/>
     </row>
@@ -37343,11 +37337,11 @@
         <v>18</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="17">
-        <v>46288.497916666667</v>
+        <v>46301.510416666664</v>
       </c>
       <c r="E21" s="7"/>
     </row>
@@ -37374,7 +37368,9 @@
       <c r="A24" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="16"/>
+      <c r="B24" s="16" t="s">
+        <v>41</v>
+      </c>
       <c r="C24" s="16"/>
       <c r="D24" s="17"/>
       <c r="E24" s="3"/>
@@ -37383,7 +37379,9 @@
       <c r="A25" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="10"/>
+      <c r="B25" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="C25" s="16"/>
       <c r="D25" s="17"/>
       <c r="E25" s="7"/>

--- a/capstone/sprint4/26-10-sprint-4-initial-metrics.xlsx
+++ b/capstone/sprint4/26-10-sprint-4-initial-metrics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fawzm\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowan\SoftwareEngineering\capstone\Stone-Ocean-Backlogs\capstone\sprint4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A5E381-367D-4578-8B4D-C4DEA9C21BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABFA62F-4287-4F8A-8249-BDF6A24402AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11442" yWindow="0" windowWidth="11676" windowHeight="13038" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example" sheetId="8" r:id="rId1"/>
@@ -533,7 +533,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26F2F5C-9428-EA43-9432-B11B4A37F6BD}">
   <dimension ref="A1:I1003"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -541,7 +541,7 @@
     <col min="7" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.5">
+    <row r="1" spans="1:9" ht="23.1">
       <c r="A1" s="13" t="s">
         <v>12</v>
       </c>
@@ -600,7 +600,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:9" ht="146">
+    <row r="8" spans="1:9" ht="145.5">
       <c r="A8" s="4" t="s">
         <v>0</v>
       </c>
@@ -11666,7 +11666,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.5">
+    <row r="1" spans="1:9" ht="23.1">
       <c r="A1" s="13" t="s">
         <v>12</v>
       </c>
@@ -17989,7 +17989,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0AC37C3-57FD-E44A-8B5F-68D0EAC49E65}">
   <dimension ref="A1:I1008"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -17998,7 +17998,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.5">
+    <row r="1" spans="1:9" ht="23.1">
       <c r="A1" s="13" t="str">
         <f>Sprint4!A1</f>
         <v>Capacity, Commited, Effort, and Delivered Metric</v>
@@ -24335,7 +24335,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D22623D9-D265-E341-9D40-D4F8180816A9}">
   <dimension ref="A1:I1008"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -24344,7 +24344,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.5">
+    <row r="1" spans="1:9" ht="23.1">
       <c r="A1" s="13" t="str">
         <f>Sprint4!A1</f>
         <v>Capacity, Commited, Effort, and Delivered Metric</v>
@@ -30681,7 +30681,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE28E1FE-DF56-8B47-AF8A-1EC59E1B4672}">
   <dimension ref="A1:I1008"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -30690,7 +30690,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.5">
+    <row r="1" spans="1:9" ht="23.1">
       <c r="A1" s="13" t="str">
         <f>Sprint4!A1</f>
         <v>Capacity, Commited, Effort, and Delivered Metric</v>
@@ -37027,7 +37027,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14211EDA-4B61-5345-86E3-D319343FC73C}">
   <dimension ref="A1:I1008"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
     <col min="2" max="5" width="5.25" customWidth="1"/>
@@ -37036,7 +37036,7 @@
     <col min="10" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.5">
+    <row r="1" spans="1:9" ht="23.1">
       <c r="A1" s="13" t="str">
         <f>Sprint4!A1</f>
         <v>Capacity, Commited, Effort, and Delivered Metric</v>
@@ -37128,10 +37128,10 @@
         <v>36</v>
       </c>
       <c r="B9" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C9" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
@@ -37154,10 +37154,10 @@
         <v>35</v>
       </c>
       <c r="B10" s="7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C10" s="7">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
